--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A8D0EA0-008E-44EF-8DC1-9B1F1036973F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953E0503-21DC-41D5-8DAC-4B09F19C2E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="28695" yWindow="-6270" windowWidth="16410" windowHeight="14145" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
-    <sheet name="DT_Texture" sheetId="1" r:id="rId1"/>
+    <sheet name="Default" sheetId="1" r:id="rId1"/>
+    <sheet name="MainTitle" sheetId="2" r:id="rId2"/>
+    <sheet name="Loading" sheetId="4" r:id="rId3"/>
+    <sheet name="Equipment" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="34">
-  <si>
-    <t>Type</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
   <si>
     <t>Id</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Extra</t>
   </si>
   <si>
-    <t>Texture</t>
-  </si>
-  <si>
     <t>COMPONENT_TYPE_TEXTURE_DEFAULT</t>
   </si>
   <si>
@@ -73,15 +70,6 @@
     <t>../../Client/Bin/Resources/Textures/UI/MainTitle/MainTitle_Text%d.png</t>
   </si>
   <si>
-    <t>COMPONENT_TYPE_TEXTURE_PLAYER</t>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Textures/Clip_Icon%d.png</t>
-  </si>
-  <si>
-    <t>COMPONENT_TYPE_TEXTURE_MONSTER</t>
-  </si>
-  <si>
     <t>COMPONENT_TYPE_TEXTURE_LOADING</t>
   </si>
   <si>
@@ -122,13 +110,53 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/MainTitle/T_UI_TitleMenu_Btn_Effect%d_BC.png</t>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_EQUIPMENT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Fcility_Customize_UP.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Static</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Common_RoleItemWindow_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Common_RoleItem_WinTitle_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Party_NameBG_Def_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Title_BG_01_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Title_Symbol_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_00_Def_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_05_Def_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,6 +313,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -714,8 +750,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1073,10 +1112,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="67.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1092,300 +1134,428 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE98167-7E76-4554-9D23-FD70CC444C72}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.75" customWidth="1"/>
+    <col min="2" max="2" width="78.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8294D36A-57D2-484B-A580-427489953197}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.625" customWidth="1"/>
+    <col min="2" max="2" width="78.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40.125" customWidth="1"/>
+    <col min="2" max="2" width="84.625" customWidth="1"/>
+    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="16.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>31</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953E0503-21DC-41D5-8DAC-4B09F19C2E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87F4BE0-ABD8-4248-ADAB-E1ACDA49C9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-6270" windowWidth="16410" windowHeight="14145" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -149,6 +149,10 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_05_Def_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_02_Sel_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1420,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.125" customWidth="1"/>
@@ -1558,6 +1562,20 @@
         <v>31</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87F4BE0-ABD8-4248-ADAB-E1ACDA49C9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D1597A-551B-4622-9A98-2F186593B9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -153,6 +153,10 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_02_Sel_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_00_Sel_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1424,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.125" customWidth="1"/>
@@ -1576,6 +1580,20 @@
         <v>31</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D1597A-551B-4622-9A98-2F186593B9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40331B1C-5F81-4F0F-9303-83327C2EC568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
     <sheet name="MainTitle" sheetId="2" r:id="rId2"/>
     <sheet name="Loading" sheetId="4" r:id="rId3"/>
     <sheet name="Equipment" sheetId="3" r:id="rId4"/>
+    <sheet name="Skill" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
   <si>
     <t>Id</t>
   </si>
@@ -157,6 +158,10 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_00_Sel_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_SKILL_GAUGE</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +169,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,6 +335,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -758,11 +770,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,10 +1135,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="67.125" customWidth="1"/>
+    <col min="1" max="1" width="51.625" customWidth="1"/>
+    <col min="2" max="2" width="72.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1173,13 +1189,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1187,13 +1203,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1204,40 +1220,12 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1598,4 +1586,68 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="49.625" customWidth="1"/>
+    <col min="2" max="2" width="75.875" customWidth="1"/>
+    <col min="3" max="4" width="19.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40331B1C-5F81-4F0F-9303-83327C2EC568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D09C806-C95E-4049-800D-49668CF45515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>COMPONENT_TYPE_TEXTURE_LOADING</t>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Textures/UI/Loading_Screen/Textures/T_UI_LoadingScreen_%03d_BC.png</t>
   </si>
   <si>
     <t>COMPONENT_TYPE_TEXTURE_SKILL_ICON</t>
@@ -162,6 +159,14 @@
   </si>
   <si>
     <t>COMPONENT_TYPE_TEXTURE_SKILL_GAUGE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/TextUI/Common_Textures/Menu_Title/T_ui_Title_Logo_CharMake_BC_LOCL.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Loading_Screen/Textures/T_UI_LoadingScreen_%d_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1189,10 +1194,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1203,10 +1208,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1217,10 +1222,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1308,7 +1313,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1317,7 +1322,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1325,7 +1330,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1346,7 +1351,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.625" customWidth="1"/>
-    <col min="2" max="2" width="78.875" customWidth="1"/>
+    <col min="2" max="2" width="88.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1371,10 +1376,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1399,10 +1404,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1416,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.125" customWidth="1"/>
@@ -1444,142 +1449,156 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>30</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1617,10 +1636,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2">
         <v>2</v>
@@ -1631,10 +1650,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2">
         <v>5</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D09C806-C95E-4049-800D-49668CF45515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EEDDFA-7E47-4517-B74C-5F9A14FAED42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -167,6 +167,14 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Loading_Screen/Textures/T_UI_LoadingScreen_%d_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_Btn_02_Def_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_DailogBG_Purchase_Product_Base_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1421,7 +1429,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.125" customWidth="1"/>
@@ -1598,6 +1606,34 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EEDDFA-7E47-4517-B74C-5F9A14FAED42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A58E93C-ADEF-4776-A488-4E1F7F576199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="Equipment" sheetId="3" r:id="rId4"/>
     <sheet name="Skill" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -175,6 +175,38 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Menu_DailogBG_Purchase_Product_Base_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_SKILL_SUB</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_ShinobiTool_Kunai_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_Clone_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_WEAPON_TYPE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_RollTextIcon_iya.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_RollTextIcon_mam.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_RollTextIcon_sem.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_RollTextIcon_sha.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1148,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
@@ -1242,9 +1274,66 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1645,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.625" customWidth="1"/>
@@ -1699,7 +1788,32 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A58E93C-ADEF-4776-A488-4E1F7F576199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766CA6E2-975B-41B5-B034-3887F8A25EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
   <si>
     <t>Id</t>
   </si>
@@ -207,6 +207,30 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_RollTextIcon_sha.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_Hit_Digit_%d.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_Hit_Small_LOCL.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_Hit_Text_LOCL_0.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_KO_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_ANNOUNCE_HIT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_ANNOUNCE_DIGIT</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1180,7 +1204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
@@ -1327,6 +1351,62 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766CA6E2-975B-41B5-B034-3887F8A25EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB6EE1-B68E-491C-A22F-8EEFAC889035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="62">
   <si>
     <t>Id</t>
   </si>
@@ -231,6 +231,17 @@
   </si>
   <si>
     <t>COMPONENT_TYPE_TEXTURE_ANNOUNCE_DIGIT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_TARGET</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/TargetCursol/Textures/T_UI_TargetCursol_Effect1.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/TargetCursol/Textures/T_UI_TargetCursol_Lock_Effect.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1204,11 +1215,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
-    <col min="2" max="2" width="72.25" customWidth="1"/>
+    <col min="2" max="2" width="96.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1407,6 +1418,34 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB6EE1-B68E-491C-A22F-8EEFAC889035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E0B206-CD12-40EC-83CF-756755A66E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -242,6 +242,50 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/ingame/TargetCursol/Textures/T_UI_TargetCursol_Lock_Effect.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_PARTICLE_SNOW</t>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_PARTICLE_EXPLOSION</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Snow/Snow.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_Hit_FX2.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_PARTICLE_HIT</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Effects/Textures/Hit/T_EFF_Hit_02_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>T_EFF_Rasengan_02_M</t>
+  </si>
+  <si>
+    <t>T_EFF_Rasengan_04_M</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>T_EFF_Rasengan_05_M</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/Rasengan/Textures/T_EFF_Rasengan_02_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/Rasengan/Textures/T_EFF_Rasengan_04_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/Rasengan/Textures/T_EFF_Rasengan_05_M.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1215,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
@@ -1446,6 +1490,48 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1853,7 +1939,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.625" customWidth="1"/>
@@ -1934,6 +2020,51 @@
         <v>30</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E0B206-CD12-40EC-83CF-756755A66E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B390492-239D-48D4-8F5F-BCF30F51E29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -286,6 +286,14 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Skills/Rasengan/Textures/T_EFF_Rasengan_05_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_TRAIL</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Effects/Textures/Traill/T_EFF_Trail_01_M.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1939,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.625" customWidth="1"/>
@@ -2063,7 +2071,24 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B390492-239D-48D4-8F5F-BCF30F51E29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26920282-1E64-47C9-927C-BE0F4688BDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="3390" yWindow="1065" windowWidth="20700" windowHeight="11850" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -294,6 +294,10 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Effects/Textures/Traill/T_EFF_Trail_01_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Roll_Selected_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1731,11 +1735,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.125" customWidth="1"/>
-    <col min="2" max="2" width="84.625" customWidth="1"/>
+    <col min="2" max="2" width="110.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="4" max="4" width="16.625" customWidth="1"/>
   </cols>
@@ -1936,6 +1940,20 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26920282-1E64-47C9-927C-BE0F4688BDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04195A78-48E7-4542-B3D7-F1F855F94F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="1065" windowWidth="20700" windowHeight="11850" activeTab="3" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="87">
   <si>
     <t>Id</t>
   </si>
@@ -298,6 +298,46 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Roll_Selected_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Effects/Textures/Traill/T_EFF_Trail_02_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_SWORD_TRAIL</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_00_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_01_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_02_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_03_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_05_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_04_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_WEP_Eff_ChakraKatana_B_01_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_WEP_Eff_D51NJ3_Noise_Line_02_M.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1271,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
@@ -1544,6 +1584,118 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2103,10 +2255,18 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04195A78-48E7-4542-B3D7-F1F855F94F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A42C28-469D-4BC4-84C3-EB4C9EAB9759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
     <sheet name="MainTitle" sheetId="2" r:id="rId2"/>
     <sheet name="Loading" sheetId="4" r:id="rId3"/>
     <sheet name="Equipment" sheetId="3" r:id="rId4"/>
-    <sheet name="Skill" sheetId="5" r:id="rId5"/>
+    <sheet name="SkySphere" sheetId="6" r:id="rId5"/>
+    <sheet name="Skill" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="103">
   <si>
     <t>Id</t>
   </si>
@@ -134,10 +135,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Title_BG_01_BC.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Title_Symbol_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -338,6 +335,72 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/Noise/T_WEP_Eff_D51NJ3_Noise_Line_02_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_MONSTER_HP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_BOSS_HP</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Boss/T_UI_Boss_Gauge1.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/CreateCharacterUI.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_SKY_SPHERE</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_AMVLLG_DenseCloudySky_N.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_AMVLLG_RainStormSky_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Cloud_middle_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Cloud_middle_N.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Cloud_side_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Cloud_side_N.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Cloud_Tile_01_M2.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Cloud_Tile_01_N2.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Clouds2_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Moon_Mask_01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_SKY_Base_01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Stars_BC_01.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1311,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
@@ -1407,10 +1470,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
         <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>49</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1421,10 +1484,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1435,10 +1498,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1449,10 +1512,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1463,10 +1526,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1477,10 +1540,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1491,10 +1554,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1505,10 +1568,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1519,10 +1582,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1533,10 +1596,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1547,10 +1610,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1561,10 +1624,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1575,10 +1638,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s">
         <v>66</v>
-      </c>
-      <c r="B19" t="s">
-        <v>67</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1589,10 +1652,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
         <v>78</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1603,10 +1666,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1617,10 +1680,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1631,10 +1694,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1645,10 +1708,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1659,10 +1722,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1673,10 +1736,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1687,15 +1750,43 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>86</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1870,7 +1961,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1974,7 +2065,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1988,7 +2079,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2002,7 +2093,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2016,7 +2107,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2030,7 +2121,7 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2044,7 +2135,7 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2058,7 +2149,7 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2072,7 +2163,7 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2086,7 +2177,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2100,7 +2191,7 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2116,6 +2207,207 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{223E5455-F230-4CDE-9CF1-770C7B008F78}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2144,7 +2436,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>17</v>
@@ -2172,10 +2464,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2186,10 +2478,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -2200,10 +2492,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -2214,10 +2506,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -2228,10 +2520,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -2242,10 +2534,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -2256,10 +2548,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A42C28-469D-4BC4-84C3-EB4C9EAB9759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289E7047-BB7F-4ED6-A74B-20499C67C3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -179,10 +179,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_ShinobiTool_Kunai_BC.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_Clone_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -401,6 +397,10 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/SkySphere/Textures/T_Stars_BC_01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_ShinobiTool_WindmillShuriken_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
         <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
         <v>58</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
         <v>65</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
         <v>77</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
         <v>87</v>
-      </c>
-      <c r="B29" t="s">
-        <v>88</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2065,7 +2065,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2191,7 +2191,7 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
         <v>90</v>
-      </c>
-      <c r="B2" t="s">
-        <v>91</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2347,10 +2347,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2413,7 +2413,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.625" customWidth="1"/>
-    <col min="2" max="2" width="75.875" customWidth="1"/>
+    <col min="2" max="2" width="88.25" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2467,7 +2467,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2481,7 +2481,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289E7047-BB7F-4ED6-A74B-20499C67C3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7563BD9B-E9E4-4544-81CE-04D7AE1DC8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="105">
   <si>
     <t>Id</t>
   </si>
@@ -401,6 +401,14 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/T_UI_ShinobiTool_WindmillShuriken_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Skill_Icon/T_UI_Skill_Kirin_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Skill_Icon/T_UI_SP_ShinsuSenju_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2409,7 +2417,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.625" customWidth="1"/>
@@ -2456,7 +2464,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -2559,6 +2567,37 @@
       <c r="D10" s="2" t="s">
         <v>30</v>
       </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7563BD9B-E9E4-4544-81CE-04D7AE1DC8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAFF63D-D43D-41D7-AE76-0349D9225320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="Loading" sheetId="4" r:id="rId3"/>
     <sheet name="Equipment" sheetId="3" r:id="rId4"/>
     <sheet name="SkySphere" sheetId="6" r:id="rId5"/>
-    <sheet name="Skill" sheetId="5" r:id="rId6"/>
+    <sheet name="Mission" sheetId="7" r:id="rId6"/>
+    <sheet name="Skill" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="119">
   <si>
     <t>Id</t>
   </si>
@@ -345,10 +346,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>../../Client/Bin/Resources/Textures/UI/Equipment/CreateCharacterUI.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>COMPONENT_TYPE_TEXTURE_SKY_SPHERE</t>
   </si>
   <si>
@@ -409,6 +406,65 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Skill_Icon/T_UI_SP_ShinsuSenju_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Dialog/Textures/T_UI_RewardList_Base_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_ui_Title_BG_01_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Dialog/Textures/T_UI_RewardList_TxtBase_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Dialog/Textures/T_UI_RewardList_Kumo%d_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Fcility_Customize.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_MISSION</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/TextUI/ingame/Announce/Textures/Fight_End.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/TextUI/ingame/Announce/Textures/Fight_Start.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/TextUI/ingame/Announce/Textures/Mission_Start.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_MISSION</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/MissionTitle_Base.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_RadialLine_01_Additive_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_RadialLine_02_Additive_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_RadialLineAdditive_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_07_M.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1382,11 +1438,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
-    <col min="2" max="2" width="96.125" customWidth="1"/>
+    <col min="2" max="2" width="107.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1795,6 +1851,62 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1986,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.125" customWidth="1"/>
@@ -2073,7 +2185,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2205,6 +2317,62 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2243,10 +2411,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
         <v>89</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2257,10 +2425,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2271,10 +2439,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2285,10 +2453,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2299,10 +2467,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2313,10 +2481,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2327,10 +2495,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2341,10 +2509,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2355,10 +2523,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2369,10 +2537,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2383,10 +2551,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2397,10 +2565,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2416,6 +2584,95 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CECF604-8A00-427D-B9BA-2EDD972CBC8F}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="101.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2475,7 +2732,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2573,7 +2830,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -2587,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAFF63D-D43D-41D7-AE76-0349D9225320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B669ABD-6374-448F-86CA-6EA7AD9C999A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="SkySphere" sheetId="6" r:id="rId5"/>
     <sheet name="Mission" sheetId="7" r:id="rId6"/>
     <sheet name="Skill" sheetId="5" r:id="rId7"/>
+    <sheet name="Boss" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="122">
   <si>
     <t>Id</t>
   </si>
@@ -465,6 +466,18 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/Noise/T_EFF_Noise_Line_07_M.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Boss/Pain_Icon.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Boss/Boss_Text.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/life_gauge_masc_Body.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1438,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
@@ -1842,10 +1855,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1859,7 +1872,7 @@
         <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1873,7 +1886,7 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1884,29 +1897,15 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2860,4 +2859,92 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171F04D1-03F7-48F3-8BBA-21499BAEFDE0}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B669ABD-6374-448F-86CA-6EA7AD9C999A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371132C6-F2BB-4027-B0CB-BD8AB3B27E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="131">
   <si>
     <t>Id</t>
   </si>
@@ -478,6 +478,41 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/PlayerStats/life_gauge_masc_Body.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_KO</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_KO_BG_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_TIMER</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Timer/Decimal%d.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Timer/Timer0.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_HALO</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/Announce/Textures/T_UI_Announce_Halo_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/ingame/TargetCursol/Textures/T_UI_TargetCursol_Lock3.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_LOCK_ON</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1451,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C4155-217D-4740-8089-8F246AA52F62}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.625" customWidth="1"/>
@@ -1906,6 +1941,104 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371132C6-F2BB-4027-B0CB-BD8AB3B27E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17C36F3-C320-408D-9765-BA25DF380F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="136">
   <si>
     <t>Id</t>
   </si>
@@ -513,6 +513,25 @@
   </si>
   <si>
     <t>COMPONENT_TYPE_TEXTURE_LOCK_ON</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Minimap/T_UI_Flag_Blue_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/TextUI/ingame/Announce/Textures/Last_Finish.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/TextUI/ingame/Announce/Textures/MissionTitle_Base.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_TEXTURE_MISSION_MARKER</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Minimap/T_UI_Boss_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2717,10 +2736,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CECF604-8A00-427D-B9BA-2EDD972CBC8F}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="101.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.75" bestFit="1" customWidth="1"/>
   </cols>
@@ -2796,6 +2815,62 @@
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17C36F3-C320-408D-9765-BA25DF380F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA2FE86-1957-4F54-B312-63151C166733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="137">
   <si>
     <t>Id</t>
   </si>
@@ -402,10 +402,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>../../Client/Bin/Resources/Textures/UI/Skill_Icon/T_UI_Skill_Kirin_BC.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>../../Client/Bin/Resources/Textures/UI/Skill_Icon/T_UI_SP_ShinsuSenju_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -532,6 +528,14 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Textures/UI/Minimap/T_UI_Boss_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Equipment/T_UI_Weapon_InfoWindow_BC.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Textures/UI/Skill_Icon/T_UI_Skill_D31NJ2_BC.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1912,7 +1916,7 @@
         <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1926,7 +1930,7 @@
         <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1940,7 +1944,7 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1954,7 +1958,7 @@
         <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1965,7 +1969,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
@@ -1979,10 +1983,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" t="s">
         <v>122</v>
-      </c>
-      <c r="B34" t="s">
-        <v>123</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1993,10 +1997,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" t="s">
         <v>124</v>
-      </c>
-      <c r="B35" t="s">
-        <v>125</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -2007,10 +2011,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -2021,10 +2025,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" t="s">
         <v>127</v>
-      </c>
-      <c r="B37" t="s">
-        <v>128</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2035,10 +2039,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -2049,7 +2053,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B39" t="s">
         <v>59</v>
@@ -2249,7 +2253,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5099ABA-1BAA-4011-9CAA-9DE70369DED4}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.125" customWidth="1"/>
@@ -2336,7 +2340,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2476,7 +2480,7 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2490,7 +2494,7 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2504,7 +2508,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18">
         <v>4</v>
@@ -2518,12 +2522,26 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19">
         <v>4</v>
       </c>
       <c r="D19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2763,10 +2781,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -2777,10 +2795,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -2791,10 +2809,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -2805,10 +2823,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -2819,10 +2837,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2833,10 +2851,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -2847,10 +2865,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2861,10 +2879,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" t="s">
         <v>134</v>
-      </c>
-      <c r="B9" t="s">
-        <v>135</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2881,7 +2899,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DF49EF-EB13-418E-B9B2-485CA38A4654}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.625" customWidth="1"/>
@@ -3037,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -3051,7 +3069,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -3059,9 +3077,6 @@
       <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -3114,7 +3129,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3128,7 +3143,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3142,7 +3157,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5">
         <v>1</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA2FE86-1957-4F54-B312-63151C166733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DF64A9-4C86-4C87-9B96-00D1467D80CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
+    <workbookView xWindow="1950" yWindow="2415" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{E1BA714A-44F4-4B9F-B605-6C062A1AF184}"/>
   </bookViews>
   <sheets>
     <sheet name="Default" sheetId="1" r:id="rId1"/>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>111</v>
